--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_151_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_151_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M2" t="n">
         <v>7</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
         <v>11</v>
@@ -904,12 +904,12 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
@@ -1531,7 +1531,7 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -1923,16 +1923,16 @@
         <v>14</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X20" t="n">
         <v>2</v>
@@ -2119,16 +2119,16 @@
         <v>21</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X21" t="n">
         <v>6</v>
@@ -2315,16 +2315,16 @@
         <v>4</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" t="n">
         <v>2</v>
@@ -2517,10 +2517,10 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X23" t="n">
         <v>7</v>
@@ -2903,16 +2903,16 @@
         <v>42</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X25" t="n">
         <v>9</v>
@@ -3099,16 +3099,16 @@
         <v>24</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X26" t="n">
         <v>9</v>
@@ -3494,7 +3494,7 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>120</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X30" t="n">
         <v>37</v>
@@ -4292,7 +4292,7 @@
         <v>10</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -4491,13 +4491,13 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X36" t="n">
         <v>9</v>
@@ -4684,10 +4684,10 @@
         <v>9</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -4883,7 +4883,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -5076,16 +5076,16 @@
         <v>13</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X39" t="n">
         <v>2</v>
@@ -5278,10 +5278,10 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
         <v>4</v>
@@ -5664,7 +5664,7 @@
         <v>4</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -6059,7 +6059,7 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -6448,7 +6448,7 @@
         <v>11</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -6784,16 +6784,16 @@
         <v>116</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X48" t="n">
         <v>28</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_151_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_151_EL.xlsx
@@ -674,10 +674,10 @@
         <v>7</v>
       </c>
       <c r="N2" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="O2" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="P2" t="n">
         <v>6</v>
@@ -833,10 +833,10 @@
         <v>11</v>
       </c>
       <c r="N3" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="O3" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="P3" t="n">
         <v>4</v>
@@ -854,17 +854,17 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V3" t="n">
         <v>12</v>
       </c>
       <c r="W3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>87.50</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>48.00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1935,14 +1935,14 @@
         <v>1</v>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA20" t="n">
@@ -2131,10 +2131,10 @@
         <v>1</v>
       </c>
       <c r="X21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
@@ -2523,10 +2523,10 @@
         <v>3</v>
       </c>
       <c r="X23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2915,10 +2915,10 @@
         <v>2</v>
       </c>
       <c r="X25" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Y25" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
@@ -3111,10 +3111,10 @@
         <v>2</v>
       </c>
       <c r="X26" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Y26" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
@@ -3503,14 +3503,14 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA28" t="n">
@@ -3839,10 +3839,10 @@
         <v>10</v>
       </c>
       <c r="X30" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="Y30" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
@@ -4340,22 +4340,22 @@
         <v>1</v>
       </c>
       <c r="AH35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AJ35" t="n">
         <v>2</v>
       </c>
       <c r="AK35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
@@ -4500,14 +4500,14 @@
         <v>1</v>
       </c>
       <c r="X36" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y36" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="AA36" t="n">
@@ -4696,14 +4696,14 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y37" t="n">
         <v>5</v>
       </c>
-      <c r="Y37" t="n">
-        <v>6</v>
-      </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="AA37" t="n">
@@ -4892,10 +4892,10 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
@@ -6068,10 +6068,10 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
@@ -6796,14 +6796,14 @@
         <v>2</v>
       </c>
       <c r="X48" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="Y48" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="AA48" t="n">
@@ -6832,22 +6832,22 @@
         <v>1</v>
       </c>
       <c r="AH48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="AJ48" t="n">
         <v>12</v>
       </c>
       <c r="AK48" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
